--- a/example_output/spreadsheets/indirect_costs_1.xlsx
+++ b/example_output/spreadsheets/indirect_costs_1.xlsx
@@ -457,7 +457,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>202001</v>
+        <v>202401</v>
       </c>
       <c r="B2" t="n">
         <v>1</v>
@@ -474,7 +474,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>202002</v>
+        <v>202402</v>
       </c>
       <c r="B3" t="n">
         <v>1</v>
@@ -491,7 +491,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>202003</v>
+        <v>202403</v>
       </c>
       <c r="B4" t="n">
         <v>1</v>
@@ -508,7 +508,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>202004</v>
+        <v>202404</v>
       </c>
       <c r="B5" t="n">
         <v>1</v>
@@ -525,7 +525,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>202005</v>
+        <v>202405</v>
       </c>
       <c r="B6" t="n">
         <v>1</v>
@@ -542,7 +542,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>202006</v>
+        <v>202406</v>
       </c>
       <c r="B7" t="n">
         <v>1</v>
@@ -559,7 +559,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>202007</v>
+        <v>202407</v>
       </c>
       <c r="B8" t="n">
         <v>1</v>
